--- a/survey_templates/032_star_wars_fan_survey--survey_templates.xlsx
+++ b/survey_templates/032_star_wars_fan_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Millennium_Falcon</t>
+          <t>Millennium Falcon</t>
         </is>
       </c>
     </row>
@@ -1322,29 +1322,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dagobah</t>
+          <t>hoth</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dagobah</t>
+          <t>Hoth</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>favorite_planet_choices</t>
+          <t>favorite_ship_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hoth</t>
+          <t>millennium_falcon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hoth</t>
+          <t>Millennium Falcon</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>millennium_falcon</t>
+          <t>x-wing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Millennium_Falcon</t>
+          <t>X-Wing</t>
         </is>
       </c>
     </row>
@@ -1373,29 +1373,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>x-wing</t>
+          <t>y-wing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>X-Wing</t>
+          <t>Y-Wing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>favorite_ship_choices</t>
+          <t>favorite_squadron_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>y-wing</t>
+          <t>rebel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Y-Wing</t>
+          <t>Rebel</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rebel</t>
+          <t>imperial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Imperial</t>
         </is>
       </c>
     </row>
@@ -1424,27 +1424,10 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>imperial</t>
+          <t>jedi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Imperial</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>favorite_squadron_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>jedi</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>Jedi</t>
         </is>
